--- a/campus-placement/qa/C-3-Transactional-Flow-and-Cross-Role-Visibility.xlsx
+++ b/campus-placement/qa/C-3-Transactional-Flow-and-Cross-Role-Visibility.xlsx
@@ -602,15 +602,11 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="P2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -688,15 +684,11 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="P3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -774,15 +766,11 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="P4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -860,15 +848,11 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="P5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -946,15 +930,11 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="P6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1032,15 +1012,11 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="P7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1118,15 +1094,11 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="P8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1204,15 +1176,11 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="P9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1290,15 +1258,11 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="P10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1376,15 +1340,11 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="P11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1462,15 +1422,11 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="P12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1548,15 +1504,11 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="P13" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
